--- a/MULTILAYER/DADES_NAPLES/graph_metrics/multilayer/global_graph_metrics_MULTILAYER.xlsx
+++ b/MULTILAYER/DADES_NAPLES/graph_metrics/multilayer/global_graph_metrics_MULTILAYER.xlsx
@@ -462,16 +462,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9466713140467061</v>
+        <v>0.8516904844893691</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4570815513747527</v>
+        <v>0.5090103767581621</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9733356570233531</v>
+        <v>0.9258452422446846</v>
       </c>
       <c r="E2" t="n">
-        <v>1.053328685953294</v>
+        <v>1.148309515510631</v>
       </c>
     </row>
     <row r="3">
@@ -481,16 +481,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9478912513070756</v>
+        <v>0.8494248867201115</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5097845360101461</v>
+        <v>0.5372188945052961</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9739456256535378</v>
+        <v>0.9247124433600558</v>
       </c>
       <c r="E3" t="n">
-        <v>1.052108748692924</v>
+        <v>1.150575113279888</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.948326943185779</v>
+        <v>0.8505576856047403</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5507752652897517</v>
+        <v>0.5797413944677838</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9741634715928895</v>
+        <v>0.9252788428023702</v>
       </c>
       <c r="E4" t="n">
-        <v>1.051673056814221</v>
+        <v>1.14944231439526</v>
       </c>
     </row>
     <row r="5">
@@ -519,16 +519,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9406587661205995</v>
+        <v>0.8428023701638201</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4702608551068704</v>
+        <v>0.4755004549276803</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9703293830602998</v>
+        <v>0.92140118508191</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0593412338794</v>
+        <v>1.15719762983618</v>
       </c>
     </row>
     <row r="6">
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9482398048100383</v>
+        <v>0.851167654234925</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5198469688357451</v>
+        <v>0.5607307917545667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9741199024050192</v>
+        <v>0.9255838271174626</v>
       </c>
       <c r="E6" t="n">
-        <v>1.051760195189962</v>
+        <v>1.148832345765075</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9482398048100383</v>
+        <v>0.8514290693621471</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4503341940893428</v>
+        <v>0.5035685595196003</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9741199024050192</v>
+        <v>0.9257145346810736</v>
       </c>
       <c r="E7" t="n">
-        <v>1.051760195189962</v>
+        <v>1.148570930637853</v>
       </c>
     </row>
     <row r="8">
@@ -576,16 +576,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9457999302892994</v>
+        <v>0.8481178110840014</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5143959041427432</v>
+        <v>0.5686787086069059</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9728999651446497</v>
+        <v>0.9240589055420007</v>
       </c>
       <c r="E8" t="n">
-        <v>1.054200069710701</v>
+        <v>1.151882188915999</v>
       </c>
     </row>
     <row r="9">
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9314220982920879</v>
+        <v>0.8372255141164169</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4090169113503839</v>
+        <v>0.4552306187725984</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9657110491460439</v>
+        <v>0.9186127570582084</v>
       </c>
       <c r="E9" t="n">
-        <v>1.068577901707912</v>
+        <v>1.162774485883583</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9063262460787731</v>
+        <v>0.8400139421401185</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3662079475739964</v>
+        <v>0.4433404266088463</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9531631230393866</v>
+        <v>0.9200069710700592</v>
       </c>
       <c r="E10" t="n">
-        <v>1.093673753921227</v>
+        <v>1.159986057859882</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9393516904844894</v>
+        <v>0.8443708609271523</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4421629372875639</v>
+        <v>0.5069722379477188</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9696758452422447</v>
+        <v>0.9221854304635762</v>
       </c>
       <c r="E11" t="n">
-        <v>1.060648309515511</v>
+        <v>1.155629139072848</v>
       </c>
     </row>
     <row r="12">
@@ -652,16 +652,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9491111885674451</v>
+        <v>0.8509933774834437</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5179556790217618</v>
+        <v>0.543194945821015</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9745555942837225</v>
+        <v>0.9254966887417219</v>
       </c>
       <c r="E12" t="n">
-        <v>1.050888811432555</v>
+        <v>1.149006622516556</v>
       </c>
     </row>
     <row r="13">
@@ -671,16 +671,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9481526664342976</v>
+        <v>0.851167654234925</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5416936729023801</v>
+        <v>0.5638310752254471</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9740763332171488</v>
+        <v>0.9255838271174626</v>
       </c>
       <c r="E13" t="n">
-        <v>1.051847333565702</v>
+        <v>1.148832345765075</v>
       </c>
     </row>
     <row r="14">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8120425235273615</v>
+        <v>0.747298710352039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.361110037801671</v>
+        <v>0.3564988649751452</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9060212617636807</v>
+        <v>0.8736493551760195</v>
       </c>
       <c r="E14" t="n">
-        <v>1.187957476472639</v>
+        <v>1.252701289647961</v>
       </c>
     </row>
     <row r="15">
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9458870686650401</v>
+        <v>0.8491634715928895</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5022025813795171</v>
+        <v>0.525978455761807</v>
       </c>
       <c r="D15" t="n">
-        <v>0.97294353433252</v>
+        <v>0.9245817357964448</v>
       </c>
       <c r="E15" t="n">
-        <v>1.05411293133496</v>
+        <v>1.15083652840711</v>
       </c>
     </row>
     <row r="16">
@@ -728,16 +728,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9459742070407807</v>
+        <v>0.8502962704775183</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4449175563521416</v>
+        <v>0.4916055810585868</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9729871035203904</v>
+        <v>0.9251481352387592</v>
       </c>
       <c r="E16" t="n">
-        <v>1.054025792959219</v>
+        <v>1.149703729522482</v>
       </c>
     </row>
     <row r="17">
@@ -747,16 +747,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9282851167654235</v>
+        <v>0.8353956082258627</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3948802120613366</v>
+        <v>0.4410602317721615</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9641425583827118</v>
+        <v>0.9176978041129313</v>
       </c>
       <c r="E17" t="n">
-        <v>1.071714883234576</v>
+        <v>1.164604391774137</v>
       </c>
     </row>
     <row r="18">
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9461484837922621</v>
+        <v>0.8467235970721506</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5092507790162938</v>
+        <v>0.5349972611856483</v>
       </c>
       <c r="D18" t="n">
-        <v>0.973074241896131</v>
+        <v>0.9233617985360753</v>
       </c>
       <c r="E18" t="n">
-        <v>1.053851516207738</v>
+        <v>1.153276402927849</v>
       </c>
     </row>
     <row r="19">
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.828860230045312</v>
+        <v>0.7482572324851865</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3364584640846442</v>
+        <v>0.4040755741217367</v>
       </c>
       <c r="D19" t="n">
-        <v>0.914430115022656</v>
+        <v>0.8741286162425932</v>
       </c>
       <c r="E19" t="n">
-        <v>1.171139769954688</v>
+        <v>1.251742767514814</v>
       </c>
     </row>
     <row r="20">
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9484140815615197</v>
+        <v>0.8520390379923318</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5706219220712104</v>
+        <v>0.5840920048612948</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9742070407807598</v>
+        <v>0.9260195189961659</v>
       </c>
       <c r="E20" t="n">
-        <v>1.05158591843848</v>
+        <v>1.147960962007668</v>
       </c>
     </row>
     <row r="21">
@@ -823,16 +823,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9482398048100383</v>
+        <v>0.8487277797141861</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5631078758385185</v>
+        <v>0.6023992730943405</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9741199024050192</v>
+        <v>0.9243638898570931</v>
       </c>
       <c r="E21" t="n">
-        <v>1.051760195189962</v>
+        <v>1.151272220285814</v>
       </c>
     </row>
     <row r="22">
@@ -842,16 +842,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9471070059254095</v>
+        <v>0.8486406413384454</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5084027440524254</v>
+        <v>0.5610824351957528</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9735535029627048</v>
+        <v>0.9243203206692228</v>
       </c>
       <c r="E22" t="n">
-        <v>1.05289299407459</v>
+        <v>1.151359358661554</v>
       </c>
     </row>
     <row r="23">
@@ -861,16 +861,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9455385151620774</v>
+        <v>0.8512547926106657</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4502295312433048</v>
+        <v>0.506444790294822</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9727692575810387</v>
+        <v>0.9256273963053329</v>
       </c>
       <c r="E23" t="n">
-        <v>1.054461484837923</v>
+        <v>1.148745207389334</v>
       </c>
     </row>
     <row r="24">
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9400487974904148</v>
+        <v>0.8466364586964099</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5059154146009259</v>
+        <v>0.5419737283886769</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9700243987452074</v>
+        <v>0.923318229348205</v>
       </c>
       <c r="E24" t="n">
-        <v>1.059951202509585</v>
+        <v>1.15336354130359</v>
       </c>
     </row>
     <row r="25">
@@ -899,16 +899,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9491111885674451</v>
+        <v>0.8507319623562217</v>
       </c>
       <c r="C25" t="n">
-        <v>0.496784557034187</v>
+        <v>0.5399610518686135</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9745555942837225</v>
+        <v>0.9253659811781109</v>
       </c>
       <c r="E25" t="n">
-        <v>1.050888811432555</v>
+        <v>1.149268037643778</v>
       </c>
     </row>
     <row r="26">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9450156849076333</v>
+        <v>0.8498605785988149</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4943155981921651</v>
+        <v>0.5260661754477656</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9725078424538166</v>
+        <v>0.9249302892994075</v>
       </c>
       <c r="E26" t="n">
-        <v>1.054984315092367</v>
+        <v>1.150139421401185</v>
       </c>
     </row>
     <row r="27">
@@ -937,16 +937,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9368246775880098</v>
+        <v>0.8421924015336354</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5506801599724568</v>
+        <v>0.5890705880099162</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9684123387940049</v>
+        <v>0.9210962007668178</v>
       </c>
       <c r="E27" t="n">
-        <v>1.06317532241199</v>
+        <v>1.157807598466364</v>
       </c>
     </row>
     <row r="28">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9471070059254095</v>
+        <v>0.8484663645869641</v>
       </c>
       <c r="C28" t="n">
-        <v>0.5824021786373851</v>
+        <v>0.6006587054824728</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9735535029627048</v>
+        <v>0.9242331822934821</v>
       </c>
       <c r="E28" t="n">
-        <v>1.05289299407459</v>
+        <v>1.151533635413036</v>
       </c>
     </row>
     <row r="29">
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9417044266294876</v>
+        <v>0.8495991634715929</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4308808460771271</v>
+        <v>0.4899392774945023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9708522133147438</v>
+        <v>0.9247995817357965</v>
       </c>
       <c r="E29" t="n">
-        <v>1.058295573370512</v>
+        <v>1.150400836528407</v>
       </c>
     </row>
     <row r="30">
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9465841756709655</v>
+        <v>0.8510805158591844</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4820504257991047</v>
+        <v>0.5387148367480536</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9732920878354827</v>
+        <v>0.9255402579295922</v>
       </c>
       <c r="E30" t="n">
-        <v>1.053415824329035</v>
+        <v>1.148919484140816</v>
       </c>
     </row>
     <row r="31">
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9412687347507842</v>
+        <v>0.8423666782851168</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4510396359721256</v>
+        <v>0.4820091224041287</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9706343673753921</v>
+        <v>0.9211833391425583</v>
       </c>
       <c r="E31" t="n">
-        <v>1.058731265249216</v>
+        <v>1.157633321714883</v>
       </c>
     </row>
     <row r="32">
@@ -1032,16 +1032,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9417915650052283</v>
+        <v>0.8459393516904845</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5337327201583225</v>
+        <v>0.5464005678416208</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9708957825026141</v>
+        <v>0.9229696758452423</v>
       </c>
       <c r="E32" t="n">
-        <v>1.058208434994772</v>
+        <v>1.154060648309515</v>
       </c>
     </row>
     <row r="33">
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9470198675496688</v>
+        <v>0.8518647612408504</v>
       </c>
       <c r="C33" t="n">
-        <v>0.509173785450033</v>
+        <v>0.5546457650576633</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9735099337748344</v>
+        <v>0.9259323806204253</v>
       </c>
       <c r="E33" t="n">
-        <v>1.052980132450331</v>
+        <v>1.148135238759149</v>
       </c>
     </row>
     <row r="34">
@@ -1070,16 +1070,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9420529801324503</v>
+        <v>0.8466364586964099</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4430029533088932</v>
+        <v>0.499112613284132</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9710264900662252</v>
+        <v>0.923318229348205</v>
       </c>
       <c r="E34" t="n">
-        <v>1.05794701986755</v>
+        <v>1.15336354130359</v>
       </c>
     </row>
     <row r="35">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9478912513070756</v>
+        <v>0.8514290693621471</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5494847923900356</v>
+        <v>0.5864317542354891</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9739456256535378</v>
+        <v>0.9257145346810736</v>
       </c>
       <c r="E35" t="n">
-        <v>1.052108748692924</v>
+        <v>1.148570930637853</v>
       </c>
     </row>
     <row r="36">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9326420355524573</v>
+        <v>0.8271174625304984</v>
       </c>
       <c r="C36" t="n">
-        <v>0.3888229699860032</v>
+        <v>0.4166006884424659</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9663210177762287</v>
+        <v>0.9135587312652492</v>
       </c>
       <c r="E36" t="n">
-        <v>1.067357964447543</v>
+        <v>1.172882537469502</v>
       </c>
     </row>
     <row r="37">
@@ -1127,16 +1127,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9489369118159637</v>
+        <v>0.8519518996165911</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5987728442202664</v>
+        <v>0.6330622200663559</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9744684559079819</v>
+        <v>0.9259759498082956</v>
       </c>
       <c r="E37" t="n">
-        <v>1.051063088184036</v>
+        <v>1.148048100383409</v>
       </c>
     </row>
     <row r="38">
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9388288602300453</v>
+        <v>0.8471592889508539</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3843745609052883</v>
+        <v>0.4486991081613471</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9694144301150227</v>
+        <v>0.923579644475427</v>
       </c>
       <c r="E38" t="n">
-        <v>1.061171139769955</v>
+        <v>1.152840711049146</v>
       </c>
     </row>
     <row r="39">
@@ -1165,16 +1165,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9437086092715232</v>
+        <v>0.8483792262112234</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4702918709178177</v>
+        <v>0.5388818238524047</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9718543046357616</v>
+        <v>0.9241896131056118</v>
       </c>
       <c r="E39" t="n">
-        <v>1.056291390728477</v>
+        <v>1.151620773788776</v>
       </c>
     </row>
     <row r="40">
@@ -1184,16 +1184,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9439700243987452</v>
+        <v>0.8465493203206692</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4871492038459858</v>
+        <v>0.52425562418988</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9719850121993726</v>
+        <v>0.9232746601603347</v>
       </c>
       <c r="E40" t="n">
-        <v>1.056029975601255</v>
+        <v>1.153450679679331</v>
       </c>
     </row>
     <row r="41">
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9340362495643081</v>
+        <v>0.8428895085395608</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4249473501589534</v>
+        <v>0.4895988921532352</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9670181247821541</v>
+        <v>0.9214447542697805</v>
       </c>
       <c r="E41" t="n">
-        <v>1.065963750435692</v>
+        <v>1.157110491460439</v>
       </c>
     </row>
     <row r="42">
@@ -1222,16 +1222,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9286336702683862</v>
+        <v>0.8292959219240154</v>
       </c>
       <c r="C42" t="n">
-        <v>0.3680979482590477</v>
+        <v>0.4200681477402166</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9643168351341931</v>
+        <v>0.9146479609620076</v>
       </c>
       <c r="E42" t="n">
-        <v>1.071366329731614</v>
+        <v>1.170704078075985</v>
       </c>
     </row>
     <row r="43">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9346462181944929</v>
+        <v>0.8333914255838272</v>
       </c>
       <c r="C43" t="n">
-        <v>0.4382092794979185</v>
+        <v>0.4873529856373455</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9673231090972464</v>
+        <v>0.9166957127919135</v>
       </c>
       <c r="E43" t="n">
-        <v>1.065353781805507</v>
+        <v>1.166608574416173</v>
       </c>
     </row>
     <row r="44">
@@ -1260,16 +1260,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9460613454165214</v>
+        <v>0.8468978738236319</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4792362699521382</v>
+        <v>0.5216368747152859</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9730306727082607</v>
+        <v>0.923448936911816</v>
       </c>
       <c r="E44" t="n">
-        <v>1.053938654583479</v>
+        <v>1.153102126176368</v>
       </c>
     </row>
     <row r="45">
@@ -1279,16 +1279,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9402230742418961</v>
+        <v>0.8433252004182642</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4277946144676821</v>
+        <v>0.478058853384991</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9701115371209481</v>
+        <v>0.9216626002091322</v>
       </c>
       <c r="E45" t="n">
-        <v>1.059776925758104</v>
+        <v>1.156674799581736</v>
       </c>
     </row>
     <row r="46">
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.929505054025793</v>
+        <v>0.8428895085395608</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4583419703357224</v>
+        <v>0.4871041001638716</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9647525270128965</v>
+        <v>0.9214447542697805</v>
       </c>
       <c r="E46" t="n">
-        <v>1.070494945974207</v>
+        <v>1.157110491460439</v>
       </c>
     </row>
     <row r="47">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9458870686650401</v>
+        <v>0.8495120250958522</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4955330869945416</v>
+        <v>0.5165685607632161</v>
       </c>
       <c r="D47" t="n">
-        <v>0.97294353433252</v>
+        <v>0.9247560125479261</v>
       </c>
       <c r="E47" t="n">
-        <v>1.05411293133496</v>
+        <v>1.150487974904148</v>
       </c>
     </row>
     <row r="48">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9465841756709655</v>
+        <v>0.8499477169745556</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4821884163233583</v>
+        <v>0.5233966556813986</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9732920878354827</v>
+        <v>0.9249738584872778</v>
       </c>
       <c r="E48" t="n">
-        <v>1.053415824329035</v>
+        <v>1.150052283025444</v>
       </c>
     </row>
     <row r="49">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.933252004182642</v>
+        <v>0.8383583130010457</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4824318595013252</v>
+        <v>0.5219412917230745</v>
       </c>
       <c r="D49" t="n">
-        <v>0.966626002091321</v>
+        <v>0.9191791565005228</v>
       </c>
       <c r="E49" t="n">
-        <v>1.066747995817358</v>
+        <v>1.161641686998954</v>
       </c>
     </row>
     <row r="50">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9449285465318926</v>
+        <v>0.8475078424538166</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5026769416048186</v>
+        <v>0.5327639749759349</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9724642732659463</v>
+        <v>0.9237539212269084</v>
       </c>
       <c r="E50" t="n">
-        <v>1.055071453468107</v>
+        <v>1.152492157546183</v>
       </c>
     </row>
     <row r="51">
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.945364238410596</v>
+        <v>0.8484663645869641</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4787103000329021</v>
+        <v>0.5226754373207946</v>
       </c>
       <c r="D51" t="n">
-        <v>0.972682119205298</v>
+        <v>0.9242331822934821</v>
       </c>
       <c r="E51" t="n">
-        <v>1.054635761589404</v>
+        <v>1.151533635413036</v>
       </c>
     </row>
     <row r="52">
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9322934820494946</v>
+        <v>0.8451551063088184</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4097119688691125</v>
+        <v>0.4395234965426482</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9661467410247473</v>
+        <v>0.9225775531544091</v>
       </c>
       <c r="E52" t="n">
-        <v>1.067706517950505</v>
+        <v>1.154844893691182</v>
       </c>
     </row>
     <row r="53">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9446671314046706</v>
+        <v>0.8493377483443708</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4700692329658553</v>
+        <v>0.4848396288199129</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9723335657023353</v>
+        <v>0.9246688741721855</v>
       </c>
       <c r="E53" t="n">
-        <v>1.055332868595329</v>
+        <v>1.150662251655629</v>
       </c>
     </row>
     <row r="54">
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9441443011502265</v>
+        <v>0.847682119205298</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4692100947638247</v>
+        <v>0.5198343484718961</v>
       </c>
       <c r="D54" t="n">
-        <v>0.9720721505751133</v>
+        <v>0.9238410596026491</v>
       </c>
       <c r="E54" t="n">
-        <v>1.055855698849773</v>
+        <v>1.152317880794702</v>
       </c>
     </row>
     <row r="55">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9449285465318926</v>
+        <v>0.8450679679330777</v>
       </c>
       <c r="C55" t="n">
-        <v>0.485507477436194</v>
+        <v>0.5313072116395333</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9724642732659463</v>
+        <v>0.9225339839665389</v>
       </c>
       <c r="E55" t="n">
-        <v>1.055071453468107</v>
+        <v>1.154932032066922</v>
       </c>
     </row>
     <row r="56">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9401359358661554</v>
+        <v>0.8428895085395608</v>
       </c>
       <c r="C56" t="n">
-        <v>0.5394813349862437</v>
+        <v>0.5590497035131838</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9700679679330777</v>
+        <v>0.9214447542697805</v>
       </c>
       <c r="E56" t="n">
-        <v>1.059864064133845</v>
+        <v>1.157110491460439</v>
       </c>
     </row>
     <row r="57">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9446671314046706</v>
+        <v>0.847682119205298</v>
       </c>
       <c r="C57" t="n">
-        <v>0.4832376700402251</v>
+        <v>0.5346248168501435</v>
       </c>
       <c r="D57" t="n">
-        <v>0.9723335657023353</v>
+        <v>0.9238410596026491</v>
       </c>
       <c r="E57" t="n">
-        <v>1.055332868595329</v>
+        <v>1.152317880794702</v>
       </c>
     </row>
     <row r="58">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9472812826768909</v>
+        <v>0.8518647612408504</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4910356391658217</v>
+        <v>0.5413088538434012</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9736406413384454</v>
+        <v>0.9259323806204253</v>
       </c>
       <c r="E58" t="n">
-        <v>1.052718717323109</v>
+        <v>1.148135238759149</v>
       </c>
     </row>
     <row r="59">
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9410944579993029</v>
+        <v>0.8464621819449285</v>
       </c>
       <c r="C59" t="n">
-        <v>0.4477594432499957</v>
+        <v>0.4969457522593693</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9705472289996514</v>
+        <v>0.9232310909724643</v>
       </c>
       <c r="E59" t="n">
-        <v>1.058905542000697</v>
+        <v>1.153537818055071</v>
       </c>
     </row>
     <row r="60">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9441443011502265</v>
+        <v>0.8483792262112234</v>
       </c>
       <c r="C60" t="n">
-        <v>0.4468437844539218</v>
+        <v>0.5163647447450515</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9720721505751133</v>
+        <v>0.9241896131056118</v>
       </c>
       <c r="E60" t="n">
-        <v>1.055855698849773</v>
+        <v>1.151620773788776</v>
       </c>
     </row>
     <row r="61">
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9430986406413384</v>
+        <v>0.844196584175671</v>
       </c>
       <c r="C61" t="n">
-        <v>0.4918652396402222</v>
+        <v>0.5282602009184144</v>
       </c>
       <c r="D61" t="n">
-        <v>0.9715493203206692</v>
+        <v>0.9220982920878354</v>
       </c>
       <c r="E61" t="n">
-        <v>1.056901359358662</v>
+        <v>1.155803415824329</v>
       </c>
     </row>
     <row r="62">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9455385151620774</v>
+        <v>0.8489891948414081</v>
       </c>
       <c r="C62" t="n">
-        <v>0.5420178742129647</v>
+        <v>0.5966870029138288</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9727692575810387</v>
+        <v>0.9244945974207041</v>
       </c>
       <c r="E62" t="n">
-        <v>1.054461484837923</v>
+        <v>1.151010805158592</v>
       </c>
     </row>
     <row r="63">
@@ -1621,16 +1621,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.9382188915998606</v>
+        <v>0.8451551063088184</v>
       </c>
       <c r="C63" t="n">
-        <v>0.4956091483275293</v>
+        <v>0.5388900432040328</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9691094457999303</v>
+        <v>0.9225775531544091</v>
       </c>
       <c r="E63" t="n">
-        <v>1.061781108400139</v>
+        <v>1.154844893691182</v>
       </c>
     </row>
     <row r="64">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9452771000348553</v>
+        <v>0.8518647612408504</v>
       </c>
       <c r="C64" t="n">
-        <v>0.4376798551556946</v>
+        <v>0.4938171648281444</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9726385500174277</v>
+        <v>0.9259323806204253</v>
       </c>
       <c r="E64" t="n">
-        <v>1.054722899965145</v>
+        <v>1.148135238759149</v>
       </c>
     </row>
     <row r="65">
@@ -1659,16 +1659,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9449285465318926</v>
+        <v>0.8470721505751133</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4947933046930523</v>
+        <v>0.5347857382465763</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9724642732659463</v>
+        <v>0.9235360752875567</v>
       </c>
       <c r="E65" t="n">
-        <v>1.055071453468107</v>
+        <v>1.152927849424887</v>
       </c>
     </row>
     <row r="66">
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9458870686650401</v>
+        <v>0.850644823980481</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5015024189900107</v>
+        <v>0.5307448338152213</v>
       </c>
       <c r="D66" t="n">
-        <v>0.97294353433252</v>
+        <v>0.9253224119902405</v>
       </c>
       <c r="E66" t="n">
-        <v>1.05411293133496</v>
+        <v>1.149355176019519</v>
       </c>
     </row>
     <row r="67">
@@ -1697,16 +1697,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9445799930289299</v>
+        <v>0.8467235970721506</v>
       </c>
       <c r="C67" t="n">
-        <v>0.4693424731204575</v>
+        <v>0.5024843250984936</v>
       </c>
       <c r="D67" t="n">
-        <v>0.972289996514465</v>
+        <v>0.9233617985360753</v>
       </c>
       <c r="E67" t="n">
-        <v>1.05542000697107</v>
+        <v>1.153276402927849</v>
       </c>
     </row>
     <row r="68">
@@ -1716,16 +1716,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.945625653537818</v>
+        <v>0.850644823980481</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5041436583481214</v>
+        <v>0.5728970176888551</v>
       </c>
       <c r="D68" t="n">
-        <v>0.972812826768909</v>
+        <v>0.9253224119902405</v>
       </c>
       <c r="E68" t="n">
-        <v>1.054374346462182</v>
+        <v>1.149355176019519</v>
       </c>
     </row>
     <row r="69">
@@ -1735,16 +1735,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9455385151620774</v>
+        <v>0.8489020564656675</v>
       </c>
       <c r="C69" t="n">
-        <v>0.466259254746083</v>
+        <v>0.5068334210825414</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9727692575810387</v>
+        <v>0.9244510282328338</v>
       </c>
       <c r="E69" t="n">
-        <v>1.054461484837923</v>
+        <v>1.151097943534332</v>
       </c>
     </row>
     <row r="70">
@@ -1754,16 +1754,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9458870686650401</v>
+        <v>0.8505576856047403</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4790979877929427</v>
+        <v>0.5214505803729623</v>
       </c>
       <c r="D70" t="n">
-        <v>0.97294353433252</v>
+        <v>0.9252788428023702</v>
       </c>
       <c r="E70" t="n">
-        <v>1.05411293133496</v>
+        <v>1.14944231439526</v>
       </c>
     </row>
     <row r="71">
@@ -1773,16 +1773,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.9463227605437434</v>
+        <v>0.8513419309864064</v>
       </c>
       <c r="C71" t="n">
-        <v>0.525903638125211</v>
+        <v>0.5532702529838186</v>
       </c>
       <c r="D71" t="n">
-        <v>0.9731613802718717</v>
+        <v>0.9256709654932032</v>
       </c>
       <c r="E71" t="n">
-        <v>1.053677239456257</v>
+        <v>1.148658069013594</v>
       </c>
     </row>
     <row r="72">
@@ -1792,16 +1792,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.9465841756709655</v>
+        <v>0.8497734402230742</v>
       </c>
       <c r="C72" t="n">
-        <v>0.5059749607434063</v>
+        <v>0.5560995060710773</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9732920878354827</v>
+        <v>0.9248867201115372</v>
       </c>
       <c r="E72" t="n">
-        <v>1.053415824329035</v>
+        <v>1.150226559776926</v>
       </c>
     </row>
     <row r="73">
@@ -1811,16 +1811,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.9376089229696758</v>
+        <v>0.8395782502614151</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5469393017822369</v>
+        <v>0.5848135212634867</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9688044614848379</v>
+        <v>0.9197891251307075</v>
       </c>
       <c r="E73" t="n">
-        <v>1.062391077030324</v>
+        <v>1.160421749738585</v>
       </c>
     </row>
     <row r="74">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.9431857790170791</v>
+        <v>0.8455907981875218</v>
       </c>
       <c r="C74" t="n">
-        <v>0.4944418126624525</v>
+        <v>0.5228922193686955</v>
       </c>
       <c r="D74" t="n">
-        <v>0.9715928895085396</v>
+        <v>0.9227953990937608</v>
       </c>
       <c r="E74" t="n">
-        <v>1.056814220982921</v>
+        <v>1.154409201812478</v>
       </c>
     </row>
     <row r="75">
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.9393516904844894</v>
+        <v>0.8438480306727083</v>
       </c>
       <c r="C75" t="n">
-        <v>0.4385617986663757</v>
+        <v>0.4807711316748434</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9696758452422447</v>
+        <v>0.9219240153363542</v>
       </c>
       <c r="E75" t="n">
-        <v>1.060648309515511</v>
+        <v>1.156151969327292</v>
       </c>
     </row>
     <row r="76">
@@ -1868,16 +1868,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.9454513767863367</v>
+        <v>0.8495120250958522</v>
       </c>
       <c r="C76" t="n">
-        <v>0.4765346769291076</v>
+        <v>0.5298175296203572</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9727256883931683</v>
+        <v>0.9247560125479261</v>
       </c>
       <c r="E76" t="n">
-        <v>1.054548623213663</v>
+        <v>1.150487974904148</v>
       </c>
     </row>
     <row r="77">
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.9462356221680028</v>
+        <v>0.8489020564656675</v>
       </c>
       <c r="C77" t="n">
-        <v>0.5229051600505399</v>
+        <v>0.5750079052757895</v>
       </c>
       <c r="D77" t="n">
-        <v>0.9731178110840014</v>
+        <v>0.9244510282328338</v>
       </c>
       <c r="E77" t="n">
-        <v>1.053764377831997</v>
+        <v>1.151097943534332</v>
       </c>
     </row>
     <row r="78">
@@ -1906,16 +1906,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.9475426978041129</v>
+        <v>0.8499477169745556</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5067587786968371</v>
+        <v>0.5513767348416119</v>
       </c>
       <c r="D78" t="n">
-        <v>0.9737713489020564</v>
+        <v>0.9249738584872778</v>
       </c>
       <c r="E78" t="n">
-        <v>1.052457302195887</v>
+        <v>1.150052283025444</v>
       </c>
     </row>
     <row r="79">
@@ -1925,16 +1925,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.9424886720111537</v>
+        <v>0.8340885325897526</v>
       </c>
       <c r="C79" t="n">
-        <v>0.4960767360078527</v>
+        <v>0.5182820474743711</v>
       </c>
       <c r="D79" t="n">
-        <v>0.9712443360055768</v>
+        <v>0.9170442662948762</v>
       </c>
       <c r="E79" t="n">
-        <v>1.057511327988846</v>
+        <v>1.165911467410248</v>
       </c>
     </row>
     <row r="80">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.9446671314046706</v>
+        <v>0.8445451376786337</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4835761216733733</v>
+        <v>0.5078292720082153</v>
       </c>
       <c r="D80" t="n">
-        <v>0.9723335657023353</v>
+        <v>0.9222725688393169</v>
       </c>
       <c r="E80" t="n">
-        <v>1.055332868595329</v>
+        <v>1.155454862321366</v>
       </c>
     </row>
     <row r="81">
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.9479783896828163</v>
+        <v>0.8516904844893691</v>
       </c>
       <c r="C81" t="n">
-        <v>0.4746071080436913</v>
+        <v>0.5198249690532202</v>
       </c>
       <c r="D81" t="n">
-        <v>0.9739891948414081</v>
+        <v>0.9258452422446846</v>
       </c>
       <c r="E81" t="n">
-        <v>1.052021610317184</v>
+        <v>1.148309515510631</v>
       </c>
     </row>
     <row r="82">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.9437957476472638</v>
+        <v>0.8433252004182642</v>
       </c>
       <c r="C82" t="n">
-        <v>0.4747284845700241</v>
+        <v>0.4954226890187257</v>
       </c>
       <c r="D82" t="n">
-        <v>0.9718978738236319</v>
+        <v>0.9216626002091322</v>
       </c>
       <c r="E82" t="n">
-        <v>1.056204252352736</v>
+        <v>1.156674799581736</v>
       </c>
     </row>
     <row r="83">
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.9396131056117114</v>
+        <v>0.8428895085395608</v>
       </c>
       <c r="C83" t="n">
-        <v>0.5487114120666953</v>
+        <v>0.5789686683585186</v>
       </c>
       <c r="D83" t="n">
-        <v>0.9698065528058557</v>
+        <v>0.9214447542697805</v>
       </c>
       <c r="E83" t="n">
-        <v>1.060386894388289</v>
+        <v>1.157110491460439</v>
       </c>
     </row>
     <row r="84">
@@ -2020,16 +2020,16 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.9457127919135587</v>
+        <v>0.8496863018473335</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5028636562006077</v>
+        <v>0.537556249624043</v>
       </c>
       <c r="D84" t="n">
-        <v>0.9728563959567794</v>
+        <v>0.9248431509236668</v>
       </c>
       <c r="E84" t="n">
-        <v>1.054287208086441</v>
+        <v>1.150313698152666</v>
       </c>
     </row>
     <row r="85">
@@ -2039,16 +2039,16 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.9451899616591146</v>
+        <v>0.8441094457999303</v>
       </c>
       <c r="C85" t="n">
-        <v>0.4830851374801847</v>
+        <v>0.4910424251793541</v>
       </c>
       <c r="D85" t="n">
-        <v>0.9725949808295573</v>
+        <v>0.9220547228999652</v>
       </c>
       <c r="E85" t="n">
-        <v>1.054810038340885</v>
+        <v>1.15589055420007</v>
       </c>
     </row>
     <row r="86">
@@ -2058,16 +2058,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.9454513767863367</v>
+        <v>0.8495991634715929</v>
       </c>
       <c r="C86" t="n">
-        <v>0.479557715243524</v>
+        <v>0.5283987348276599</v>
       </c>
       <c r="D86" t="n">
-        <v>0.9727256883931683</v>
+        <v>0.9247995817357965</v>
       </c>
       <c r="E86" t="n">
-        <v>1.054548623213663</v>
+        <v>1.150400836528407</v>
       </c>
     </row>
     <row r="87">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.9461484837922621</v>
+        <v>0.850383408853259</v>
       </c>
       <c r="C87" t="n">
-        <v>0.4835106215064259</v>
+        <v>0.5479353948927295</v>
       </c>
       <c r="D87" t="n">
-        <v>0.973074241896131</v>
+        <v>0.9251917044266295</v>
       </c>
       <c r="E87" t="n">
-        <v>1.053851516207738</v>
+        <v>1.149616591146741</v>
       </c>
     </row>
     <row r="88">
@@ -2096,16 +2096,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.9475426978041129</v>
+        <v>0.8507319623562217</v>
       </c>
       <c r="C88" t="n">
-        <v>0.5255000620087852</v>
+        <v>0.5710761779917455</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9737713489020564</v>
+        <v>0.9253659811781109</v>
       </c>
       <c r="E88" t="n">
-        <v>1.052457302195887</v>
+        <v>1.149268037643778</v>
       </c>
     </row>
     <row r="89">
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.9468455907981875</v>
+        <v>0.8477692575810387</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5034205002557413</v>
+        <v>0.5152639161650617</v>
       </c>
       <c r="D89" t="n">
-        <v>0.9734227953990937</v>
+        <v>0.9238846287905194</v>
       </c>
       <c r="E89" t="n">
-        <v>1.053154409201813</v>
+        <v>1.152230742418961</v>
       </c>
     </row>
     <row r="90">
@@ -2134,16 +2134,16 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.9405716277448588</v>
+        <v>0.8424538166608574</v>
       </c>
       <c r="C90" t="n">
-        <v>0.4682191012233899</v>
+        <v>0.4977102633253581</v>
       </c>
       <c r="D90" t="n">
-        <v>0.9702858138724294</v>
+        <v>0.9212269083304288</v>
       </c>
       <c r="E90" t="n">
-        <v>1.059428372255141</v>
+        <v>1.157546183339142</v>
       </c>
     </row>
     <row r="91">
@@ -2153,16 +2153,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.9412687347507842</v>
+        <v>0.8360055768560474</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4951457630630999</v>
+        <v>0.4729927986542819</v>
       </c>
       <c r="D91" t="n">
-        <v>0.9706343673753921</v>
+        <v>0.9180027884280237</v>
       </c>
       <c r="E91" t="n">
-        <v>1.058731265249216</v>
+        <v>1.163994423143953</v>
       </c>
     </row>
     <row r="92">
@@ -2172,16 +2172,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.9451899616591146</v>
+        <v>0.8464621819449285</v>
       </c>
       <c r="C92" t="n">
-        <v>0.4755438533767251</v>
+        <v>0.5197294178203098</v>
       </c>
       <c r="D92" t="n">
-        <v>0.9725949808295573</v>
+        <v>0.9232310909724643</v>
       </c>
       <c r="E92" t="n">
-        <v>1.054810038340885</v>
+        <v>1.153537818055071</v>
       </c>
     </row>
     <row r="93">
@@ -2191,16 +2191,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.9401359358661554</v>
+        <v>0.8453293830602998</v>
       </c>
       <c r="C93" t="n">
-        <v>0.4829624578107075</v>
+        <v>0.5175767354719507</v>
       </c>
       <c r="D93" t="n">
-        <v>0.9700679679330777</v>
+        <v>0.9226646915301498</v>
       </c>
       <c r="E93" t="n">
-        <v>1.059864064133845</v>
+        <v>1.1546706169397</v>
       </c>
     </row>
     <row r="94">
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.945364238410596</v>
+        <v>0.8486406413384454</v>
       </c>
       <c r="C94" t="n">
-        <v>0.5101203029391475</v>
+        <v>0.5518046446727423</v>
       </c>
       <c r="D94" t="n">
-        <v>0.972682119205298</v>
+        <v>0.9243203206692228</v>
       </c>
       <c r="E94" t="n">
-        <v>1.054635761589404</v>
+        <v>1.151359358661554</v>
       </c>
     </row>
     <row r="95">
@@ -2229,16 +2229,16 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.9430115022655978</v>
+        <v>0.8454165214360404</v>
       </c>
       <c r="C95" t="n">
-        <v>0.4874766547804064</v>
+        <v>0.5003770087455152</v>
       </c>
       <c r="D95" t="n">
-        <v>0.9715057511327989</v>
+        <v>0.9227082607180203</v>
       </c>
       <c r="E95" t="n">
-        <v>1.056988497734402</v>
+        <v>1.154583478563959</v>
       </c>
     </row>
     <row r="96">
@@ -2248,16 +2248,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.9451899616591146</v>
+        <v>0.8494248867201115</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4570552129007536</v>
+        <v>0.5137376884298154</v>
       </c>
       <c r="D96" t="n">
-        <v>0.9725949808295573</v>
+        <v>0.9247124433600558</v>
       </c>
       <c r="E96" t="n">
-        <v>1.054810038340885</v>
+        <v>1.150575113279888</v>
       </c>
     </row>
     <row r="97">
@@ -2267,16 +2267,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.9400487974904148</v>
+        <v>0.8397525270128965</v>
       </c>
       <c r="C97" t="n">
-        <v>0.5123546456526792</v>
+        <v>0.5080411526642213</v>
       </c>
       <c r="D97" t="n">
-        <v>0.9700243987452074</v>
+        <v>0.9198762635064482</v>
       </c>
       <c r="E97" t="n">
-        <v>1.059951202509585</v>
+        <v>1.160247472987104</v>
       </c>
     </row>
     <row r="98">
@@ -2286,16 +2286,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.9443185779017079</v>
+        <v>0.8495120250958522</v>
       </c>
       <c r="C98" t="n">
-        <v>0.4244015627797617</v>
+        <v>0.4925851697136386</v>
       </c>
       <c r="D98" t="n">
-        <v>0.9721592889508539</v>
+        <v>0.9247560125479261</v>
       </c>
       <c r="E98" t="n">
-        <v>1.055681422098292</v>
+        <v>1.150487974904148</v>
       </c>
     </row>
     <row r="99">
@@ -2305,16 +2305,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.948326943185779</v>
+        <v>0.850644823980481</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5417781535870858</v>
+        <v>0.5905498286185127</v>
       </c>
       <c r="D99" t="n">
-        <v>0.9741634715928895</v>
+        <v>0.9253224119902405</v>
       </c>
       <c r="E99" t="n">
-        <v>1.051673056814221</v>
+        <v>1.149355176019519</v>
       </c>
     </row>
     <row r="100">
@@ -2324,16 +2324,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.9446671314046706</v>
+        <v>0.8492506099686302</v>
       </c>
       <c r="C100" t="n">
-        <v>0.4727882525833563</v>
+        <v>0.5348024690801315</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9723335657023353</v>
+        <v>0.9246253049843151</v>
       </c>
       <c r="E100" t="n">
-        <v>1.055332868595329</v>
+        <v>1.15074939003137</v>
       </c>
     </row>
     <row r="101">
@@ -2343,16 +2343,16 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.941878703380969</v>
+        <v>0.8481178110840014</v>
       </c>
       <c r="C101" t="n">
-        <v>0.4560320707355005</v>
+        <v>0.5196270993511296</v>
       </c>
       <c r="D101" t="n">
-        <v>0.9709393516904845</v>
+        <v>0.9240589055420007</v>
       </c>
       <c r="E101" t="n">
-        <v>1.058121296619031</v>
+        <v>1.151882188915999</v>
       </c>
     </row>
     <row r="102">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.945625653537818</v>
+        <v>0.8494248867201115</v>
       </c>
       <c r="C102" t="n">
-        <v>0.5110582197815391</v>
+        <v>0.5360435399655777</v>
       </c>
       <c r="D102" t="n">
-        <v>0.972812826768909</v>
+        <v>0.9247124433600558</v>
       </c>
       <c r="E102" t="n">
-        <v>1.054374346462182</v>
+        <v>1.150575113279888</v>
       </c>
     </row>
     <row r="103">
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.9442314395259672</v>
+        <v>0.8462007668177065</v>
       </c>
       <c r="C103" t="n">
-        <v>0.4508456467050578</v>
+        <v>0.4949599433854528</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9721157197629836</v>
+        <v>0.9231003834088533</v>
       </c>
       <c r="E103" t="n">
-        <v>1.055768560474033</v>
+        <v>1.153799233182293</v>
       </c>
     </row>
     <row r="104">
@@ -2400,16 +2400,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.9438828860230045</v>
+        <v>0.8473335657023353</v>
       </c>
       <c r="C104" t="n">
-        <v>0.5582896745094899</v>
+        <v>0.5775634704520604</v>
       </c>
       <c r="D104" t="n">
-        <v>0.9719414430115023</v>
+        <v>0.9236667828511677</v>
       </c>
       <c r="E104" t="n">
-        <v>1.056117113976995</v>
+        <v>1.152666434297665</v>
       </c>
     </row>
     <row r="105">
@@ -2419,16 +2419,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.9465841756709655</v>
+        <v>0.8477692575810387</v>
       </c>
       <c r="C105" t="n">
-        <v>0.463349052780231</v>
+        <v>0.4909566062140802</v>
       </c>
       <c r="D105" t="n">
-        <v>0.9732920878354827</v>
+        <v>0.9238846287905194</v>
       </c>
       <c r="E105" t="n">
-        <v>1.053415824329035</v>
+        <v>1.152230742418961</v>
       </c>
     </row>
     <row r="106">
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.9437957476472638</v>
+        <v>0.8471592889508539</v>
       </c>
       <c r="C106" t="n">
-        <v>0.522246005075686</v>
+        <v>0.5402212127986296</v>
       </c>
       <c r="D106" t="n">
-        <v>0.9718978738236319</v>
+        <v>0.923579644475427</v>
       </c>
       <c r="E106" t="n">
-        <v>1.056204252352736</v>
+        <v>1.152840711049146</v>
       </c>
     </row>
   </sheetData>
